--- a/tests/utils/study_analyses/study_inputs/disciplines_spec_options.xlsx
+++ b/tests/utils/study_analyses/study_inputs/disciplines_spec_options.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexandre.scotto\Documents\GEMSEO\tests\utils\study_analyses\study_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matthias.delozzo\GEMSEO\gemseo\tests\utils\study_analyses\study_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>a</t>
   </si>
@@ -91,22 +91,16 @@
     <t>Options values</t>
   </si>
   <si>
-    <t>MDAGaussSeidel</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
     <t>my_test_scenario</t>
   </si>
   <si>
-    <t>main_mda_name</t>
-  </si>
-  <si>
     <t>main_mda_settings</t>
   </si>
   <si>
-    <t>{"max_mda_iter": 20, "warm_start": True, "tolerance": 1e-5, "over_relaxation_factor": 1.2}</t>
+    <t>MDAGaussSeidel_Settings(max_mda_iter=20, warm_start=True, tolerance=1e-5, over_relaxation_factor=1.2)</t>
   </si>
 </sst>
 </file>
@@ -142,9 +136,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -525,7 +518,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M5"/>
+  <dimension ref="B1:M3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -572,10 +565,10 @@
         <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
@@ -586,22 +579,11 @@
         <v>18</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L4" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="M5" s="1"/>
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
